--- a/dLiveChannelList.xlsx
+++ b/dLiveChannelList.xlsx
@@ -61617,7 +61617,7 @@
       <c r="AR65" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="V2:V33 G2:G65 L2:L33 Q2:Q65 AA2:AA65 AF2:AF33 AJ34 C2:C25 AK2:AK17 AP2:AP17 AU2:AU17 AY2:AY9 BC2:BC9">
+  <conditionalFormatting sqref="G2:G65 L2:L33 Q2:Q65 AA2:AA65 AF2:AF33 AJ34 C2:C25 AK2:AK17 AP2:AP17 AU2:AU17 AY2:AY9 BC2:BC9 V2:V33">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"purple"</formula>
     </cfRule>

--- a/dLiveChannelList.xlsx
+++ b/dLiveChannelList.xlsx
@@ -2349,7 +2349,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="129" min="129" style="3" width="35.84"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="true" ht="75.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" s="9" customFormat="true" ht="85.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>

--- a/dLiveChannelList.xlsx
+++ b/dLiveChannelList.xlsx
@@ -2349,7 +2349,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="129" min="129" style="3" width="35.84"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="true" ht="85.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="9" customFormat="true" ht="82.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
